--- a/AAII_Financials/Yearly/DUK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DUK_YR_FIN.xlsx
@@ -4700,13 +4700,13 @@
         <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>3138000</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>3073000</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>3008000</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
